--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_증빙매핑표_전체6분야_20261008_v2.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_증빙매핑표_전체6분야_20261008_v2.xlsx
@@ -666,6 +666,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -2105,7 +2106,11 @@
           <t>생산팀</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>이광재</t>
+        </is>
+      </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
           <t>보유</t>
